--- a/output/별첨01_MXCN1A_Factor_Return_Info.xlsx
+++ b/output/별첨01_MXCN1A_Factor_Return_Info.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D226"/>
+  <dimension ref="A1:F226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,6 +456,16 @@
           <t>cagr</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>in_portfolio</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>port_weight</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -476,6 +486,14 @@
       <c r="D2" t="n">
         <v>0.0736889690875164</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0155152824755847</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +514,14 @@
       <c r="D3" t="n">
         <v>0.0713665414583837</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0329448910188368</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -516,6 +542,14 @@
       <c r="D4" t="n">
         <v>0.0685302326117762</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0357720920074081</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -536,6 +570,14 @@
       <c r="D5" t="n">
         <v>0.0664368459963276</v>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0333382965685542</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -556,6 +598,8 @@
       <c r="D6" t="n">
         <v>0.0620794409043177</v>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -576,6 +620,8 @@
       <c r="D7" t="n">
         <v>0.0594315445620079</v>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -596,6 +642,8 @@
       <c r="D8" t="n">
         <v>0.058257375011069</v>
       </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -616,6 +664,8 @@
       <c r="D9" t="n">
         <v>0.0570977316591885</v>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -636,6 +686,8 @@
       <c r="D10" t="n">
         <v>0.0531597670172911</v>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -656,6 +708,8 @@
       <c r="D11" t="n">
         <v>0.0516579823073095</v>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -676,6 +730,14 @@
       <c r="D12" t="n">
         <v>0.0501481045468057</v>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0479589282430525</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -696,6 +758,8 @@
       <c r="D13" t="n">
         <v>0.05010651953531</v>
       </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -716,6 +780,14 @@
       <c r="D14" t="n">
         <v>0.0500045358708334</v>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0547964525957288</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -736,6 +808,8 @@
       <c r="D15" t="n">
         <v>0.0495136815716175</v>
       </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -756,6 +830,8 @@
       <c r="D16" t="n">
         <v>0.047777416953175</v>
       </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -776,6 +852,14 @@
       <c r="D17" t="n">
         <v>0.0477472089289818</v>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0213422864624267</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -796,6 +880,8 @@
       <c r="D18" t="n">
         <v>0.0473578902807456</v>
       </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -816,6 +902,14 @@
       <c r="D19" t="n">
         <v>0.0450596048083835</v>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0190645378434786</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -836,6 +930,8 @@
       <c r="D20" t="n">
         <v>0.0450271974674221</v>
       </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -856,6 +952,8 @@
       <c r="D21" t="n">
         <v>0.0435005792103331</v>
       </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -876,6 +974,8 @@
       <c r="D22" t="n">
         <v>0.043347551925108</v>
       </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -896,6 +996,8 @@
       <c r="D23" t="n">
         <v>0.04305214279175</v>
       </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -916,6 +1018,8 @@
       <c r="D24" t="n">
         <v>0.0428633856402853</v>
       </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -936,6 +1040,8 @@
       <c r="D25" t="n">
         <v>0.0427820859571674</v>
       </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -956,6 +1062,8 @@
       <c r="D26" t="n">
         <v>0.0424796707375916</v>
       </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -976,6 +1084,14 @@
       <c r="D27" t="n">
         <v>0.0421624198635528</v>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.0464467360801175</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -996,6 +1112,8 @@
       <c r="D28" t="n">
         <v>0.0420473648777623</v>
       </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1016,6 +1134,8 @@
       <c r="D29" t="n">
         <v>0.0393602438862621</v>
       </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1036,6 +1156,8 @@
       <c r="D30" t="n">
         <v>0.0387745057679835</v>
       </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1056,6 +1178,8 @@
       <c r="D31" t="n">
         <v>0.0381084390198809</v>
       </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1076,6 +1200,8 @@
       <c r="D32" t="n">
         <v>0.0378297380146637</v>
       </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1096,6 +1222,8 @@
       <c r="D33" t="n">
         <v>0.0374241584145595</v>
       </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1116,6 +1244,8 @@
       <c r="D34" t="n">
         <v>0.0369861238659501</v>
       </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1136,6 +1266,14 @@
       <c r="D35" t="n">
         <v>0.0366886357395086</v>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0.0186963655471513</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1156,6 +1294,8 @@
       <c r="D36" t="n">
         <v>0.0365979504811511</v>
       </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1176,6 +1316,14 @@
       <c r="D37" t="n">
         <v>0.0365762711690704</v>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0.0298546063087531</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1196,6 +1344,8 @@
       <c r="D38" t="n">
         <v>0.0361088083904648</v>
       </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1216,6 +1366,8 @@
       <c r="D39" t="n">
         <v>0.035644106873715</v>
       </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1236,6 +1388,14 @@
       <c r="D40" t="n">
         <v>0.0353562369976874</v>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0664622622888693</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1256,6 +1416,8 @@
       <c r="D41" t="n">
         <v>0.0350268992720701</v>
       </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1276,6 +1438,8 @@
       <c r="D42" t="n">
         <v>0.0345177969561274</v>
       </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1296,6 +1460,8 @@
       <c r="D43" t="n">
         <v>0.0339654733276004</v>
       </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1316,6 +1482,8 @@
       <c r="D44" t="n">
         <v>0.033403954443264</v>
       </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1336,6 +1504,8 @@
       <c r="D45" t="n">
         <v>0.032695166732483</v>
       </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1356,6 +1526,8 @@
       <c r="D46" t="n">
         <v>0.0323922057510681</v>
       </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1376,6 +1548,8 @@
       <c r="D47" t="n">
         <v>0.0314248675841171</v>
       </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1396,6 +1570,8 @@
       <c r="D48" t="n">
         <v>0.0311496362132552</v>
       </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1416,6 +1592,14 @@
       <c r="D49" t="n">
         <v>0.0309949683419457</v>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0.0396343090077379</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1436,6 +1620,8 @@
       <c r="D50" t="n">
         <v>0.030969888177865</v>
       </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1456,6 +1642,8 @@
       <c r="D51" t="n">
         <v>0.0305479957985925</v>
       </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1476,6 +1664,8 @@
       <c r="D52" t="n">
         <v>0.0305318685030424</v>
       </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1496,6 +1686,8 @@
       <c r="D53" t="n">
         <v>0.0302587169139985</v>
       </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1516,6 +1708,8 @@
       <c r="D54" t="n">
         <v>0.0301556969206127</v>
       </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1536,6 +1730,14 @@
       <c r="D55" t="n">
         <v>0.0294915789746486</v>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0.0505412696299291</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1556,6 +1758,8 @@
       <c r="D56" t="n">
         <v>0.0293153921113611</v>
       </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1576,6 +1780,8 @@
       <c r="D57" t="n">
         <v>0.0291474342918092</v>
       </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1596,6 +1802,8 @@
       <c r="D58" t="n">
         <v>0.0286078160025513</v>
       </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1616,6 +1824,14 @@
       <c r="D59" t="n">
         <v>0.0285693047716288</v>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0244127842934402</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1636,6 +1852,8 @@
       <c r="D60" t="n">
         <v>0.0285490008543689</v>
       </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1656,6 +1874,8 @@
       <c r="D61" t="n">
         <v>0.0285193690063048</v>
       </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1676,6 +1896,14 @@
       <c r="D62" t="n">
         <v>0.028413019645975</v>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>0.0254491488602628</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1696,6 +1924,8 @@
       <c r="D63" t="n">
         <v>0.0278288921674205</v>
       </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1716,6 +1946,8 @@
       <c r="D64" t="n">
         <v>0.0273358224606716</v>
       </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1736,6 +1968,8 @@
       <c r="D65" t="n">
         <v>0.0270901463224606</v>
       </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1756,6 +1990,8 @@
       <c r="D66" t="n">
         <v>0.0268297496225748</v>
       </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1776,6 +2012,8 @@
       <c r="D67" t="n">
         <v>0.0267097575398769</v>
       </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1796,6 +2034,8 @@
       <c r="D68" t="n">
         <v>0.0266767591243211</v>
       </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1816,6 +2056,8 @@
       <c r="D69" t="n">
         <v>0.0265037865425779</v>
       </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1836,6 +2078,8 @@
       <c r="D70" t="n">
         <v>0.0263669423444601</v>
       </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1856,6 +2100,8 @@
       <c r="D71" t="n">
         <v>0.0262740215023746</v>
       </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1876,6 +2122,8 @@
       <c r="D72" t="n">
         <v>0.0262452707054046</v>
       </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1896,6 +2144,14 @@
       <c r="D73" t="n">
         <v>0.0260121541495059</v>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>0.0135981410198242</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1916,6 +2172,8 @@
       <c r="D74" t="n">
         <v>0.0255076883154001</v>
       </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1936,6 +2194,8 @@
       <c r="D75" t="n">
         <v>0.0252308075626805</v>
       </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1956,6 +2216,8 @@
       <c r="D76" t="n">
         <v>0.0251780634625908</v>
       </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1976,6 +2238,8 @@
       <c r="D77" t="n">
         <v>0.0246837315663033</v>
       </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1996,6 +2260,8 @@
       <c r="D78" t="n">
         <v>0.0244841383540936</v>
       </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2016,6 +2282,8 @@
       <c r="D79" t="n">
         <v>0.0244376043240126</v>
       </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2036,6 +2304,8 @@
       <c r="D80" t="n">
         <v>0.0244210085666691</v>
       </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2056,6 +2326,8 @@
       <c r="D81" t="n">
         <v>0.0242746948086223</v>
       </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2076,6 +2348,8 @@
       <c r="D82" t="n">
         <v>0.0242282711992245</v>
       </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2096,6 +2370,8 @@
       <c r="D83" t="n">
         <v>0.0241550880848855</v>
       </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2116,6 +2392,8 @@
       <c r="D84" t="n">
         <v>0.0239332565037309</v>
       </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2136,6 +2414,8 @@
       <c r="D85" t="n">
         <v>0.0238022665192199</v>
       </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2156,6 +2436,8 @@
       <c r="D86" t="n">
         <v>0.0237445022016558</v>
       </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2176,6 +2458,8 @@
       <c r="D87" t="n">
         <v>0.0236563630236079</v>
       </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2196,6 +2480,8 @@
       <c r="D88" t="n">
         <v>0.0234107395414517</v>
       </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2216,6 +2502,8 @@
       <c r="D89" t="n">
         <v>0.0231352214840481</v>
       </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2236,6 +2524,8 @@
       <c r="D90" t="n">
         <v>0.0230929063704834</v>
       </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2256,6 +2546,8 @@
       <c r="D91" t="n">
         <v>0.0230028830845872</v>
       </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2276,6 +2568,8 @@
       <c r="D92" t="n">
         <v>0.0227785840557361</v>
       </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2296,6 +2590,8 @@
       <c r="D93" t="n">
         <v>0.0223305202870147</v>
       </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2316,6 +2612,8 @@
       <c r="D94" t="n">
         <v>0.0222788579025401</v>
       </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2336,6 +2634,8 @@
       <c r="D95" t="n">
         <v>0.0222590753345719</v>
       </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2356,6 +2656,8 @@
       <c r="D96" t="n">
         <v>0.0216729346252613</v>
       </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2376,6 +2678,14 @@
       <c r="D97" t="n">
         <v>0.021337788692435</v>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>0.013774556795399</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2396,6 +2706,8 @@
       <c r="D98" t="n">
         <v>0.0212908454000344</v>
       </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2416,6 +2728,8 @@
       <c r="D99" t="n">
         <v>0.0212195532912464</v>
       </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2436,6 +2750,8 @@
       <c r="D100" t="n">
         <v>0.0210553007094473</v>
       </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2456,6 +2772,8 @@
       <c r="D101" t="n">
         <v>0.0210382798924797</v>
       </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2476,6 +2794,14 @@
       <c r="D102" t="n">
         <v>0.0209606992575159</v>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>0.0525090312606919</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2496,6 +2822,8 @@
       <c r="D103" t="n">
         <v>0.0207761136315884</v>
       </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2516,6 +2844,8 @@
       <c r="D104" t="n">
         <v>0.0207642621080703</v>
       </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2536,6 +2866,8 @@
       <c r="D105" t="n">
         <v>0.0206343631601004</v>
       </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2556,6 +2888,14 @@
       <c r="D106" t="n">
         <v>0.0205766830267213</v>
       </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>0.0490907868996961</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2576,6 +2916,8 @@
       <c r="D107" t="n">
         <v>0.020461989187295</v>
       </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2596,6 +2938,8 @@
       <c r="D108" t="n">
         <v>0.0204615169312691</v>
       </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2616,6 +2960,14 @@
       <c r="D109" t="n">
         <v>0.0201001944694059</v>
       </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>0.0185039096031577</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2636,6 +2988,8 @@
       <c r="D110" t="n">
         <v>0.0199930891279809</v>
       </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2656,6 +3010,8 @@
       <c r="D111" t="n">
         <v>0.0199470644385146</v>
       </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2676,6 +3032,8 @@
       <c r="D112" t="n">
         <v>0.0198689850151823</v>
       </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2696,6 +3054,8 @@
       <c r="D113" t="n">
         <v>0.0198271500246054</v>
       </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2716,6 +3076,8 @@
       <c r="D114" t="n">
         <v>0.0196655362234277</v>
       </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2736,6 +3098,14 @@
       <c r="D115" t="n">
         <v>0.0191827045897976</v>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>0.0310707999483261</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2756,6 +3126,8 @@
       <c r="D116" t="n">
         <v>0.0191330892887922</v>
       </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2776,6 +3148,14 @@
       <c r="D117" t="n">
         <v>0.0190861344529138</v>
       </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>0.0711461889075324</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2796,6 +3176,8 @@
       <c r="D118" t="n">
         <v>0.0187614756387322</v>
       </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2816,6 +3198,8 @@
       <c r="D119" t="n">
         <v>0.0186264592875924</v>
       </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2836,6 +3220,8 @@
       <c r="D120" t="n">
         <v>0.0183931508562531</v>
       </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2856,6 +3242,8 @@
       <c r="D121" t="n">
         <v>0.0182804592173873</v>
       </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2876,6 +3264,8 @@
       <c r="D122" t="n">
         <v>0.0182462745564382</v>
       </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2896,6 +3286,8 @@
       <c r="D123" t="n">
         <v>0.0179809414672793</v>
       </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2916,6 +3308,8 @@
       <c r="D124" t="n">
         <v>0.0178961502754626</v>
       </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2936,6 +3330,8 @@
       <c r="D125" t="n">
         <v>0.0177725280906435</v>
       </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2956,6 +3352,8 @@
       <c r="D126" t="n">
         <v>0.0177621362831446</v>
       </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2976,6 +3374,14 @@
       <c r="D127" t="n">
         <v>0.0176832972517926</v>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>0.0274163200325238</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2996,6 +3402,8 @@
       <c r="D128" t="n">
         <v>0.0176535266020732</v>
       </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3016,6 +3424,8 @@
       <c r="D129" t="n">
         <v>0.0174548120019</v>
       </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3036,6 +3446,8 @@
       <c r="D130" t="n">
         <v>0.0174057576638042</v>
       </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3056,6 +3468,8 @@
       <c r="D131" t="n">
         <v>0.0174057576638042</v>
       </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3076,6 +3490,14 @@
       <c r="D132" t="n">
         <v>0.0172993547214455</v>
       </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>0.0468294947503503</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3096,6 +3518,8 @@
       <c r="D133" t="n">
         <v>0.0172907982752075</v>
       </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3116,6 +3540,8 @@
       <c r="D134" t="n">
         <v>0.0169995562516891</v>
       </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3136,6 +3562,8 @@
       <c r="D135" t="n">
         <v>0.0167669215929178</v>
       </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3156,6 +3584,8 @@
       <c r="D136" t="n">
         <v>0.0165764037071889</v>
       </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3176,6 +3606,8 @@
       <c r="D137" t="n">
         <v>0.0165094111937504</v>
       </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3196,6 +3628,8 @@
       <c r="D138" t="n">
         <v>0.0162119921968018</v>
       </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3216,6 +3650,8 @@
       <c r="D139" t="n">
         <v>0.0161573869281941</v>
       </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3236,6 +3672,8 @@
       <c r="D140" t="n">
         <v>0.015803265016111</v>
       </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3256,6 +3694,8 @@
       <c r="D141" t="n">
         <v>0.0157555950613761</v>
       </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3276,6 +3716,8 @@
       <c r="D142" t="n">
         <v>0.0155988749465136</v>
       </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3296,6 +3738,8 @@
       <c r="D143" t="n">
         <v>0.0153743385125399</v>
       </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3316,6 +3760,8 @@
       <c r="D144" t="n">
         <v>0.0151415005448669</v>
       </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3336,6 +3782,8 @@
       <c r="D145" t="n">
         <v>0.0148183948545663</v>
       </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3356,6 +3804,8 @@
       <c r="D146" t="n">
         <v>0.0148106747756169</v>
       </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3376,6 +3826,8 @@
       <c r="D147" t="n">
         <v>0.0145011868855111</v>
       </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3396,6 +3848,8 @@
       <c r="D148" t="n">
         <v>0.0144957510324148</v>
       </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3416,6 +3870,8 @@
       <c r="D149" t="n">
         <v>0.0142958583549073</v>
       </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3436,6 +3892,8 @@
       <c r="D150" t="n">
         <v>0.0136031074530713</v>
       </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3456,6 +3914,8 @@
       <c r="D151" t="n">
         <v>0.0135220280840042</v>
       </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3476,6 +3936,8 @@
       <c r="D152" t="n">
         <v>0.013357834345159</v>
       </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3496,6 +3958,8 @@
       <c r="D153" t="n">
         <v>0.0132747143834286</v>
       </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3516,6 +3980,8 @@
       <c r="D154" t="n">
         <v>0.013229642958259</v>
       </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3536,6 +4002,8 @@
       <c r="D155" t="n">
         <v>0.0132227378522902</v>
       </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3556,6 +4024,8 @@
       <c r="D156" t="n">
         <v>0.0129443391250874</v>
       </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3576,6 +4046,8 @@
       <c r="D157" t="n">
         <v>0.0127128831537282</v>
       </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3596,6 +4068,8 @@
       <c r="D158" t="n">
         <v>0.0126456070239611</v>
       </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3616,6 +4090,8 @@
       <c r="D159" t="n">
         <v>0.012175019026168</v>
       </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3636,6 +4112,8 @@
       <c r="D160" t="n">
         <v>0.0121653013883797</v>
       </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3656,6 +4134,8 @@
       <c r="D161" t="n">
         <v>0.0119661023612107</v>
       </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3676,6 +4156,8 @@
       <c r="D162" t="n">
         <v>0.0117251877994688</v>
       </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3696,6 +4178,8 @@
       <c r="D163" t="n">
         <v>0.0115906526213156</v>
       </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3716,6 +4200,8 @@
       <c r="D164" t="n">
         <v>0.0114289029591332</v>
       </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3736,6 +4222,8 @@
       <c r="D165" t="n">
         <v>0.0111378858380941</v>
       </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3756,6 +4244,8 @@
       <c r="D166" t="n">
         <v>0.0107503901000636</v>
       </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3776,6 +4266,8 @@
       <c r="D167" t="n">
         <v>0.010636732924296</v>
       </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3796,6 +4288,8 @@
       <c r="D168" t="n">
         <v>0.0105316219255577</v>
       </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3816,6 +4310,8 @@
       <c r="D169" t="n">
         <v>0.0104589950200058</v>
       </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3836,6 +4332,8 @@
       <c r="D170" t="n">
         <v>0.0104267472938717</v>
       </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3856,6 +4354,8 @@
       <c r="D171" t="n">
         <v>0.0104199033897001</v>
       </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3876,6 +4376,14 @@
       <c r="D172" t="n">
         <v>0.0102371449030493</v>
       </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>0.0240004579946317</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3896,6 +4404,8 @@
       <c r="D173" t="n">
         <v>0.009934291618834501</v>
       </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3916,6 +4426,8 @@
       <c r="D174" t="n">
         <v>0.0096887511818837</v>
       </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3936,6 +4448,8 @@
       <c r="D175" t="n">
         <v>0.0096490632871295</v>
       </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3956,6 +4470,8 @@
       <c r="D176" t="n">
         <v>0.009503883566417799</v>
       </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3976,6 +4492,8 @@
       <c r="D177" t="n">
         <v>0.0090969861439824</v>
       </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3996,6 +4514,8 @@
       <c r="D178" t="n">
         <v>0.0090567377783654</v>
       </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4016,6 +4536,8 @@
       <c r="D179" t="n">
         <v>0.008983773735802199</v>
       </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4036,6 +4558,8 @@
       <c r="D180" t="n">
         <v>0.0087653874218773</v>
       </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4056,6 +4580,8 @@
       <c r="D181" t="n">
         <v>0.008592334233548301</v>
       </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4076,6 +4602,8 @@
       <c r="D182" t="n">
         <v>0.008313312838763499</v>
       </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4096,6 +4624,8 @@
       <c r="D183" t="n">
         <v>0.0081271212180258</v>
       </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4116,6 +4646,14 @@
       <c r="D184" t="n">
         <v>0.0077231363865379</v>
       </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>0.0643982503343683</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4136,6 +4674,8 @@
       <c r="D185" t="n">
         <v>0.0073636417086087</v>
       </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4156,6 +4696,8 @@
       <c r="D186" t="n">
         <v>0.0066287839488099</v>
       </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4176,6 +4718,8 @@
       <c r="D187" t="n">
         <v>0.0064250502515863</v>
       </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4196,6 +4740,14 @@
       <c r="D188" t="n">
         <v>0.0057116859351262</v>
       </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>0.0254318132221657</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4216,6 +4768,8 @@
       <c r="D189" t="n">
         <v>0.0056142469543243</v>
       </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4236,6 +4790,8 @@
       <c r="D190" t="n">
         <v>0.005219465326016</v>
       </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4256,6 +4812,8 @@
       <c r="D191" t="n">
         <v>0.004779068770619</v>
       </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4276,6 +4834,8 @@
       <c r="D192" t="n">
         <v>0.0047054866069122</v>
       </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4296,6 +4856,8 @@
       <c r="D193" t="n">
         <v>0.0036790486997573</v>
       </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4316,6 +4878,8 @@
       <c r="D194" t="n">
         <v>0.0035290789248374</v>
       </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4336,6 +4900,8 @@
       <c r="D195" t="n">
         <v>0.0034803820956403</v>
       </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4356,6 +4922,8 @@
       <c r="D196" t="n">
         <v>0.0031730706844399</v>
       </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4376,6 +4944,8 @@
       <c r="D197" t="n">
         <v>0.0020097461812698</v>
       </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4396,6 +4966,8 @@
       <c r="D198" t="n">
         <v>0.0013692912627065</v>
       </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4416,6 +4988,8 @@
       <c r="D199" t="n">
         <v>0.000840928279767</v>
       </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4436,6 +5010,8 @@
       <c r="D200" t="n">
         <v>0.0005955110202533</v>
       </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4456,6 +5032,8 @@
       <c r="D201" t="n">
         <v>0.0004015328823312</v>
       </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4476,6 +5054,8 @@
       <c r="D202" t="n">
         <v>0.0003486041595033</v>
       </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4496,6 +5076,8 @@
       <c r="D203" t="n">
         <v>8.024264316031093e-05</v>
       </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4516,6 +5098,8 @@
       <c r="D204" t="n">
         <v>-0.0009201807788159001</v>
       </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4536,6 +5120,8 @@
       <c r="D205" t="n">
         <v>-0.0015268436232873</v>
       </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4556,6 +5142,8 @@
       <c r="D206" t="n">
         <v>-0.0016893997033126</v>
       </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4576,6 +5164,8 @@
       <c r="D207" t="n">
         <v>-0.0021090602014205</v>
       </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4596,6 +5186,8 @@
       <c r="D208" t="n">
         <v>-0.0036325321473705</v>
       </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4616,6 +5208,8 @@
       <c r="D209" t="n">
         <v>-0.0042578346431623</v>
       </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4636,6 +5230,8 @@
       <c r="D210" t="n">
         <v>-0.0059201163332405</v>
       </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4656,6 +5252,8 @@
       <c r="D211" t="n">
         <v>-0.006581423726837</v>
       </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4676,6 +5274,8 @@
       <c r="D212" t="n">
         <v>-0.0066234716100904</v>
       </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4696,6 +5296,8 @@
       <c r="D213" t="n">
         <v>-0.0073840381409844</v>
       </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4716,6 +5318,8 @@
       <c r="D214" t="n">
         <v>-0.0076080837344346</v>
       </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4736,6 +5340,8 @@
       <c r="D215" t="n">
         <v>-0.0076332837609839</v>
       </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4756,6 +5362,8 @@
       <c r="D216" t="n">
         <v>-0.0096436315214334</v>
       </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4776,6 +5384,8 @@
       <c r="D217" t="n">
         <v>-0.0109429408731149</v>
       </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4796,6 +5406,8 @@
       <c r="D218" t="n">
         <v>-0.0113543748197315</v>
       </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4816,6 +5428,8 @@
       <c r="D219" t="n">
         <v>-0.012306014045874</v>
       </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4836,6 +5450,8 @@
       <c r="D220" t="n">
         <v>-0.0171361662639489</v>
       </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4856,6 +5472,8 @@
       <c r="D221" t="n">
         <v>-0.0198830768927569</v>
       </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4876,6 +5494,8 @@
       <c r="D222" t="n">
         <v>-0.0218649359950832</v>
       </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4896,6 +5516,8 @@
       <c r="D223" t="n">
         <v>-0.0257717320194614</v>
       </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4916,6 +5538,8 @@
       <c r="D224" t="n">
         <v>-0.0452432150028065</v>
       </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4936,6 +5560,8 @@
       <c r="D225" t="n">
         <v>-0.0560010837473077</v>
       </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4956,6 +5582,8 @@
       <c r="D226" t="n">
         <v>-0.0597614642863782</v>
       </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
